--- a/sources/Brnensky_pohar_2026_27.xlsx
+++ b/sources/Brnensky_pohar_2026_27.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="98">
   <si>
     <t>ÚČASTNÍCI</t>
   </si>
@@ -221,13 +221,16 @@
     <t>11.</t>
   </si>
   <si>
-    <t>28.10.2026 - svátek</t>
+    <t>C - 20:00</t>
   </si>
   <si>
     <t>12.</t>
   </si>
   <si>
     <t>13.</t>
+  </si>
+  <si>
+    <t>28.10.2026 - svátek</t>
   </si>
   <si>
     <t>14.</t>
@@ -730,14 +733,14 @@
       <alignment horizontal="left" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="7" fillId="5" fontId="11" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="1" fillId="4" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
-    </xf>
     <xf borderId="4" fillId="3" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="1" fillId="4" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="7" fillId="5" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
@@ -1892,15 +1895,15 @@
       <c r="V15" s="21"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="22" t="s">
-        <v>50</v>
+      <c r="A16" s="41" t="s">
+        <v>69</v>
       </c>
       <c r="B16" s="53" t="s">
-        <v>69</v>
-      </c>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="3"/>
+        <v>25</v>
+      </c>
+      <c r="C16" s="29"/>
+      <c r="D16" s="29"/>
+      <c r="E16" s="29"/>
       <c r="F16" s="42"/>
       <c r="G16" s="50" t="s">
         <v>70</v>
@@ -1948,11 +1951,9 @@
       <c r="V16" s="21"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="27" t="s">
-        <v>51</v>
-      </c>
-      <c r="B17" s="51" t="s">
-        <v>4</v>
+      <c r="A17" s="33"/>
+      <c r="B17" s="54" t="s">
+        <v>28</v>
       </c>
       <c r="C17" s="29"/>
       <c r="D17" s="29"/>
@@ -2003,15 +2004,17 @@
       <c r="V17" s="21"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="33"/>
-      <c r="B18" s="34" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" s="29"/>
-      <c r="D18" s="29"/>
-      <c r="E18" s="29"/>
+      <c r="A18" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="B18" s="55" t="s">
+        <v>72</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="3"/>
       <c r="G18" s="50" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H18" s="44" t="s">
         <v>43</v>
@@ -2056,18 +2059,18 @@
       <c r="V18" s="21"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="41" t="s">
-        <v>56</v>
-      </c>
-      <c r="B19" s="54" t="s">
-        <v>25</v>
+      <c r="A19" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="B19" s="49" t="s">
+        <v>7</v>
       </c>
       <c r="C19" s="29"/>
       <c r="D19" s="29"/>
       <c r="E19" s="29"/>
       <c r="F19" s="42"/>
       <c r="G19" s="50" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H19" s="44" t="s">
         <v>46</v>
@@ -2113,8 +2116,8 @@
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="33"/>
-      <c r="B20" s="55" t="s">
-        <v>28</v>
+      <c r="B20" s="34" t="s">
+        <v>16</v>
       </c>
       <c r="C20" s="29"/>
       <c r="D20" s="29"/>
@@ -2163,7 +2166,7 @@
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="33"/>
-      <c r="B22" s="55" t="s">
+      <c r="B22" s="54" t="s">
         <v>31</v>
       </c>
       <c r="C22" s="29"/>
@@ -2473,7 +2476,7 @@
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="33"/>
-      <c r="B34" s="55" t="s">
+      <c r="B34" s="54" t="s">
         <v>16</v>
       </c>
       <c r="C34" s="29"/>
@@ -3444,8 +3447,8 @@
       <c r="A70" s="41" t="s">
         <v>59</v>
       </c>
-      <c r="B70" s="80" t="s">
-        <v>7</v>
+      <c r="B70" s="51" t="s">
+        <v>4</v>
       </c>
       <c r="C70" s="82"/>
       <c r="D70" s="82"/>
@@ -4048,8 +4051,8 @@
       <c r="A93" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="B93" s="53" t="s">
-        <v>74</v>
+      <c r="B93" s="55" t="s">
+        <v>75</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" s="2"/>
@@ -5345,8 +5348,8 @@
       <c r="A142" s="86" t="s">
         <v>50</v>
       </c>
-      <c r="B142" s="53" t="s">
-        <v>75</v>
+      <c r="B142" s="55" t="s">
+        <v>76</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" s="2"/>
@@ -5374,7 +5377,7 @@
         <v>51</v>
       </c>
       <c r="B143" s="88" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C143" s="89"/>
       <c r="D143" s="2"/>
@@ -5423,10 +5426,10 @@
     </row>
     <row r="145" ht="15.75" customHeight="1">
       <c r="A145" s="87" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B145" s="88" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C145" s="89"/>
       <c r="D145" s="2"/>
@@ -5478,7 +5481,7 @@
         <v>56</v>
       </c>
       <c r="B147" s="88" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C147" s="89"/>
       <c r="D147" s="2"/>
@@ -5530,7 +5533,7 @@
         <v>59</v>
       </c>
       <c r="B149" s="88" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C149" s="89"/>
       <c r="D149" s="2"/>
@@ -5582,7 +5585,7 @@
         <v>50</v>
       </c>
       <c r="B151" s="91" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C151" s="92"/>
       <c r="D151" s="92"/>
@@ -5610,7 +5613,7 @@
         <v>51</v>
       </c>
       <c r="B152" s="88" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C152" s="95"/>
       <c r="D152" s="2"/>
@@ -5658,10 +5661,10 @@
     </row>
     <row r="154" ht="15.75" customHeight="1">
       <c r="A154" s="88" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B154" s="88" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C154" s="95"/>
       <c r="D154" s="2"/>
@@ -5712,8 +5715,8 @@
       <c r="A156" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="B156" s="53" t="s">
-        <v>84</v>
+      <c r="B156" s="55" t="s">
+        <v>85</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" s="2"/>
@@ -5741,7 +5744,7 @@
         <v>51</v>
       </c>
       <c r="B157" s="97" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C157" s="98"/>
       <c r="D157" s="99"/>
@@ -5790,10 +5793,10 @@
     </row>
     <row r="159" ht="15.75" customHeight="1">
       <c r="A159" s="96" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B159" s="97" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C159" s="98"/>
       <c r="D159" s="99"/>
@@ -5844,8 +5847,8 @@
       <c r="A161" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="B161" s="53" t="s">
-        <v>87</v>
+      <c r="B161" s="55" t="s">
+        <v>88</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" s="2"/>
@@ -5870,10 +5873,10 @@
     </row>
     <row r="162" ht="15.75" customHeight="1">
       <c r="A162" s="96" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B162" s="97" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C162" s="98"/>
       <c r="D162" s="99"/>
@@ -5922,10 +5925,10 @@
     </row>
     <row r="164" ht="15.75" customHeight="1">
       <c r="A164" s="96" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B164" s="97" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C164" s="98"/>
       <c r="D164" s="99"/>
@@ -5976,8 +5979,8 @@
       <c r="A166" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="B166" s="53" t="s">
-        <v>92</v>
+      <c r="B166" s="55" t="s">
+        <v>93</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" s="2"/>
@@ -6002,10 +6005,10 @@
     </row>
     <row r="167" ht="15.75" customHeight="1">
       <c r="A167" s="96" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B167" s="102" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C167" s="103"/>
       <c r="D167" s="99"/>
@@ -6054,10 +6057,10 @@
     </row>
     <row r="169" ht="15.75" customHeight="1">
       <c r="A169" s="96" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B169" s="105" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C169" s="106"/>
       <c r="D169" s="99"/>
@@ -17481,6 +17484,18 @@
       <c r="T996" s="21"/>
       <c r="U996" s="21"/>
       <c r="V996" s="21"/>
+    </row>
+    <row r="997" ht="15.75" customHeight="1">
+      <c r="S997" s="21"/>
+      <c r="T997" s="21"/>
+      <c r="U997" s="21"/>
+      <c r="V997" s="21"/>
+    </row>
+    <row r="998" ht="15.75" customHeight="1">
+      <c r="S998" s="21"/>
+      <c r="T998" s="21"/>
+      <c r="U998" s="21"/>
+      <c r="V998" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="150">
@@ -17543,8 +17558,8 @@
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B16:E16"/>
-    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B18:E18"/>
     <mergeCell ref="A19:A20"/>
     <mergeCell ref="A21:A22"/>
     <mergeCell ref="A24:A25"/>
